--- a/Excel/cari volume, halaman, doi.xlsx
+++ b/Excel/cari volume, halaman, doi.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UNDIPA\Semester 7\Skripsi\skripsi\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KULIAH\SEMESTER 7\PROPOSAL SKRIPSI\skripsi\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{34374017-3655-4398-8C8A-63ED52EF4DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B123652-9EC2-459A-9ECD-ED705E66FFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E5FAC91A-0A8E-4CB8-968E-726A276FB5F1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{E5FAC91A-0A8E-4CB8-968E-726A276FB5F1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="32">
   <si>
     <t>No</t>
   </si>
@@ -94,13 +94,49 @@
   </si>
   <si>
     <t>DOI tidak ada</t>
+  </si>
+  <si>
+    <t>Doi</t>
+  </si>
+  <si>
+    <t>746-754</t>
+  </si>
+  <si>
+    <t>DOI: https://doi.org/10.35870/jti k.v7i4.1950</t>
+  </si>
+  <si>
+    <t>Vol. 9No.6, Desember 2025</t>
+  </si>
+  <si>
+    <t>9982-9989</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.36040/jati.v9i6.15696</t>
+  </si>
+  <si>
+    <t>59-69</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.26740/jeisbi.v4i4.57449</t>
+  </si>
+  <si>
+    <t>Vol. 4 No. 4 (2023)</t>
+  </si>
+  <si>
+    <t>187-199</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.31004/innovative.v4i3.12243</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.57152/malcom.v2i1.188</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,16 +152,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -133,11 +183,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -148,8 +214,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -462,10 +541,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDA4C600-4C72-4CE0-A58E-9032AC5302AC}">
-  <dimension ref="A1:E18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -481,8 +560,17 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -498,8 +586,13 @@
       <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="87" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -515,8 +608,15 @@
       <c r="E3" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="H3" s="5"/>
+      <c r="I3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -532,8 +632,11 @@
       <c r="E4" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+    </row>
+    <row r="5" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -549,8 +652,17 @@
       <c r="E5" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="H5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="87" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -566,8 +678,11 @@
       <c r="E6" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+    </row>
+    <row r="7" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -583,8 +698,11 @@
       <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+    </row>
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -600,8 +718,13 @@
       <c r="E8" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="H8" s="5"/>
+      <c r="I8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="5"/>
+    </row>
+    <row r="9" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -617,8 +740,11 @@
       <c r="E9" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -634,8 +760,11 @@
       <c r="E10" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+    </row>
+    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -651,8 +780,11 @@
       <c r="E11" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -668,8 +800,11 @@
       <c r="E12" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+    </row>
+    <row r="13" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -685,8 +820,11 @@
       <c r="E13" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="7"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -702,8 +840,11 @@
       <c r="E14" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -719,8 +860,11 @@
       <c r="E15" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -736,8 +880,17 @@
       <c r="E16" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H16" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -753,8 +906,11 @@
       <c r="E17" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="1:10" ht="87" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -770,8 +926,20 @@
       <c r="E18" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="6" t="s">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="J5" r:id="rId1" xr:uid="{B7B517A6-79C1-41BE-B048-06E1723A2B05}"/>
+    <hyperlink ref="J16" r:id="rId2" xr:uid="{7DDC3934-C9FB-4785-BD77-637F2F18480D}"/>
+    <hyperlink ref="H16" r:id="rId3" display="https://ejournal.unesa.ac.id/index.php/JEISBI/issue/view/2947" xr:uid="{CB7257F8-A118-489F-AD64-A1A5164E765B}"/>
+    <hyperlink ref="J18" r:id="rId4" xr:uid="{02C59EE1-D5B6-4A59-83A5-1ACB368533E5}"/>
+    <hyperlink ref="J2" r:id="rId5" xr:uid="{95DB861D-835C-47F5-BEEE-3D3371207639}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Excel/cari volume, halaman, doi.xlsx
+++ b/Excel/cari volume, halaman, doi.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KULIAH\SEMESTER 7\PROPOSAL SKRIPSI\skripsi\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UNDIPA\Semester 7\Skripsi\skripsi\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B123652-9EC2-459A-9ECD-ED705E66FFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47082F93-C07B-4BE9-8B68-1050702CE6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{E5FAC91A-0A8E-4CB8-968E-726A276FB5F1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E5FAC91A-0A8E-4CB8-968E-726A276FB5F1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="34">
   <si>
     <t>No</t>
   </si>
@@ -130,6 +130,12 @@
   </si>
   <si>
     <t>https://doi.org/10.57152/malcom.v2i1.188</t>
+  </si>
+  <si>
+    <t>done</t>
+  </si>
+  <si>
+    <t>done dengan mengakali</t>
   </si>
 </sst>
 </file>
@@ -541,10 +547,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDA4C600-4C72-4CE0-A58E-9032AC5302AC}">
-  <dimension ref="A1:J18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -570,7 +576,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="72" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -591,8 +597,11 @@
       <c r="J2" s="6" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="87" x14ac:dyDescent="0.35">
+      <c r="K2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -615,8 +624,11 @@
       <c r="J3" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -636,7 +648,7 @@
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
     </row>
-    <row r="5" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -661,8 +673,11 @@
       <c r="J5" s="6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="87" x14ac:dyDescent="0.35">
+      <c r="K5" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -682,7 +697,7 @@
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
     </row>
-    <row r="7" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -702,7 +717,7 @@
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
     </row>
-    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -723,8 +738,11 @@
         <v>26</v>
       </c>
       <c r="J8" s="5"/>
-    </row>
-    <row r="9" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="K8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -744,7 +762,7 @@
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -764,7 +782,7 @@
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
     </row>
-    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -784,7 +802,7 @@
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -804,7 +822,7 @@
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
     </row>
-    <row r="13" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -824,7 +842,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="7"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -844,7 +862,7 @@
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -864,7 +882,7 @@
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
     </row>
-    <row r="16" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" ht="72" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -889,8 +907,11 @@
       <c r="J16" s="6" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -910,7 +931,7 @@
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
     </row>
-    <row r="18" spans="1:10" ht="87" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -930,6 +951,9 @@
       <c r="I18" s="5"/>
       <c r="J18" s="6" t="s">
         <v>30</v>
+      </c>
+      <c r="K18" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
